--- a/backend/FINAL_MODULE_1_TO_4_RECONCILIATION.xlsx
+++ b/backend/FINAL_MODULE_1_TO_4_RECONCILIATION.xlsx
@@ -506,7 +506,7 @@
         <v>14200</v>
       </c>
       <c r="E5">
-        <v>323.27</v>
+        <v>173.12</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>11800</v>
       </c>
       <c r="E6">
-        <v>243.75</v>
+        <v>93.6</v>
       </c>
       <c r="F6">
         <v>0</v>
